--- a/cfg/excel/SkillCfg.xlsx
+++ b/cfg/excel/SkillCfg.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UGit\Shooting\Luban\Config\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Shooting\Luban\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17055"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="99">
   <si>
     <t>##var</t>
   </si>
@@ -331,9 +331,6 @@
   </si>
   <si>
     <t>超感知</t>
-  </si>
-  <si>
-    <t>0, 0</t>
   </si>
 </sst>
 </file>
@@ -2488,22 +2485,26 @@
       <c r="C28" s="9">
         <v>1004</v>
       </c>
-      <c r="D28" s="9"/>
+      <c r="D28" s="9" t="s">
+        <v>28</v>
+      </c>
       <c r="E28" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="F28" s="11"/>
+      <c r="F28" s="11" t="s">
+        <v>96</v>
+      </c>
       <c r="G28" s="9">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="H28" s="9" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="I28" s="9">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="J28" s="9">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="K28"/>
       <c r="L28"/>
